--- a/htr-update-fr-medication/ig/StructureDefinition-fr-medication-document.xlsx
+++ b/htr-update-fr-medication/ig/StructureDefinition-fr-medication-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="342">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T08:28:14+00:00</t>
+    <t>2026-09-04T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,17 +487,17 @@
     <t>Medication classification/category. Allows the product to be classified by various systems, e.g ATC, narcotic class, legal status of supply, etc..</t>
   </si>
   <si>
-    <t>Medication.extension:conditionnement</t>
-  </si>
-  <si>
-    <t>conditionnement</t>
+    <t>Medication.extension:characteristic</t>
+  </si>
+  <si>
+    <t>characteristic</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-characteristic|1.0.0-comment-2}
 </t>
   </si>
   <si>
-    <t>Présentation / conditionnement.</t>
+    <t>Caractéristique du médicament.</t>
   </si>
   <si>
     <t>Any characteristic of the medicinal product prescribed or dispensed (for example, price, textual package description, special program information, etc)</t>
@@ -566,10 +566,6 @@
   </si>
   <si>
     <t>This extension applies to Medication and expresses the type of the container for the product (e.g. bottle, unit-dose blister, pre-filled pen).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Medication.modifierExtension</t>
@@ -3265,7 +3261,7 @@
         <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>138</v>
@@ -3285,14 +3281,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3314,16 +3310,16 @@
         <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3372,7 +3368,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3401,10 +3397,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3427,16 +3423,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3486,7 +3482,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3504,10 +3500,10 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3515,10 +3511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3541,16 +3537,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3576,14 +3572,14 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y19" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3600,7 +3596,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3615,24 +3611,24 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3655,13 +3651,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3712,7 +3708,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3730,7 +3726,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3741,14 +3737,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3770,13 +3766,13 @@
         <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="N21" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3817,7 +3813,7 @@
         <v>135</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
@@ -3826,7 +3822,7 @@
         <v>136</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3844,7 +3840,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3855,10 +3851,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3881,19 +3877,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3918,29 +3914,29 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3958,21 +3954,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3995,19 +3991,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4056,7 +4052,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4074,21 +4070,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4114,13 +4110,13 @@
         <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4146,14 +4142,14 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4170,7 +4166,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4188,7 +4184,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4199,10 +4195,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4225,13 +4221,13 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4282,7 +4278,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4297,24 +4293,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4337,16 +4333,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4372,11 +4368,11 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4394,7 +4390,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4409,24 +4405,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4449,13 +4445,13 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4506,7 +4502,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4524,7 +4520,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4535,10 +4531,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4561,16 +4557,16 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4620,7 +4616,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4638,7 +4634,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4649,10 +4645,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4675,13 +4671,13 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4732,7 +4728,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4750,7 +4746,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4761,14 +4757,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4790,13 +4786,13 @@
         <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="N30" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4846,7 +4842,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4864,7 +4860,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4875,14 +4871,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4904,16 +4900,16 @@
         <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="N31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4962,7 +4958,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4991,10 +4987,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5017,17 +5013,17 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5064,17 +5060,17 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -5089,27 +5085,27 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5131,17 +5127,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5166,11 +5162,11 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5188,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -5203,24 +5199,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5243,13 +5239,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5300,7 +5296,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5318,7 +5314,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5329,14 +5325,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5358,13 +5354,13 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5405,7 +5401,7 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
@@ -5414,7 +5410,7 @@
         <v>136</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5432,7 +5428,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5443,10 +5439,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5469,19 +5465,19 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5530,7 +5526,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5548,21 +5544,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5585,19 +5581,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5646,7 +5642,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5664,24 +5660,24 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -5703,17 +5699,17 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5762,7 +5758,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>87</v>
@@ -5777,24 +5773,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5817,17 +5813,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5876,7 +5872,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5894,7 +5890,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5905,10 +5901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5931,13 +5927,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5988,7 +5984,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6003,24 +5999,24 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6043,13 +6039,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6100,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6118,7 +6114,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6129,14 +6125,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6158,13 +6154,13 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6205,7 +6201,7 @@
         <v>135</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
@@ -6214,7 +6210,7 @@
         <v>136</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6232,7 +6228,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6243,13 +6239,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
@@ -6271,13 +6267,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6328,7 +6324,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6357,10 +6353,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6383,13 +6379,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6440,7 +6436,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6458,7 +6454,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6469,10 +6465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6495,13 +6491,13 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6552,7 +6548,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6570,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6581,10 +6577,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6607,13 +6603,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6664,7 +6660,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6679,10 +6675,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6693,10 +6689,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6719,13 +6715,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6776,7 +6772,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6794,7 +6790,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6805,14 +6801,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6834,13 +6830,13 @@
         <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="N48" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6890,7 +6886,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6904,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6919,14 +6915,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6948,16 +6944,16 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="N49" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7006,7 +7002,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7035,10 +7031,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7061,13 +7057,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7118,7 +7114,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7133,24 +7129,24 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7173,13 +7169,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7230,7 +7226,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7245,16 +7241,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
   </sheetData>
